--- a/evaluation_metrics.xlsx
+++ b/evaluation_metrics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juhy/Desktop/verl-train/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5856546-4B46-B94C-A430-5E9E8C6A3578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08E7CD26-1FDB-B04F-8ACE-E3AE2FD793D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
   <si>
     <t>model_path</t>
   </si>
@@ -608,7 +608,7 @@
         <v>56.67</v>
       </c>
       <c r="C3">
-        <v>15258</v>
+        <v>12258</v>
       </c>
       <c r="E3">
         <v>98.48</v>
@@ -630,165 +630,32 @@
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="D4">
-        <f t="shared" ref="D4:D13" si="0">B4*SQRT(1-C4/16927)</f>
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <f t="shared" ref="G4:G13" si="1">E4*SQRT(1-F4/16927)</f>
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <f t="shared" ref="J4:J13" si="2">H4*SQRT(1-I4/16927)</f>
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <f t="shared" ref="M4:M13" si="3">K4*SQRT(1-L4/16927)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="D5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="D6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="D7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="D9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="D10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="D11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="D12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="D13">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4">
+        <v>56.67</v>
+      </c>
+      <c r="C4">
+        <v>4965</v>
+      </c>
+      <c r="E4">
+        <v>98.04</v>
+      </c>
+      <c r="F4">
+        <v>1040</v>
+      </c>
+      <c r="H4">
+        <v>93.2</v>
+      </c>
+      <c r="I4">
+        <v>1674</v>
+      </c>
+      <c r="K4">
+        <v>93.72</v>
+      </c>
+      <c r="L4">
+        <v>742</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -826,14 +693,14 @@
         <v>80.303643977178709</v>
       </c>
       <c r="K14">
-        <v>89.46</v>
+        <v>87.46</v>
       </c>
       <c r="L14">
         <v>1165</v>
       </c>
       <c r="M14">
         <f>K14*SQRT(1-L14/16927)</f>
-        <v>86.326584474600139</v>
+        <v>84.396636241320465</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -847,7 +714,7 @@
         <v>11199</v>
       </c>
       <c r="D15">
-        <f t="shared" ref="D15:D19" si="4">B15*SQRT(1-C15/16927)</f>
+        <f t="shared" ref="D15:D19" si="0">B15*SQRT(1-C15/16927)</f>
         <v>21.33155019969567</v>
       </c>
       <c r="E15">
@@ -857,7 +724,7 @@
         <v>1436</v>
       </c>
       <c r="G15">
-        <f t="shared" ref="G15:G19" si="5">E15*SQRT(1-F15/16927)</f>
+        <f t="shared" ref="G15:G19" si="1">E15*SQRT(1-F15/16927)</f>
         <v>90.268798531270377</v>
       </c>
       <c r="H15">
@@ -867,18 +734,18 @@
         <v>3036</v>
       </c>
       <c r="J15">
-        <f t="shared" ref="J15:J19" si="6">H15*SQRT(1-I15/16927)</f>
+        <f t="shared" ref="J15:J19" si="2">H15*SQRT(1-I15/16927)</f>
         <v>76.819700708652704</v>
       </c>
       <c r="K15">
-        <v>73.77</v>
+        <v>83.77</v>
       </c>
       <c r="L15">
         <v>517</v>
       </c>
       <c r="M15">
-        <f t="shared" ref="M15:M19" si="7">K15*SQRT(1-L15/16927)</f>
-        <v>72.63468825262062</v>
+        <f t="shared" ref="M15:M19" si="3">K15*SQRT(1-L15/16927)</f>
+        <v>82.480789411983594</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -892,7 +759,7 @@
         <v>3634</v>
       </c>
       <c r="D16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>32.496187748926872</v>
       </c>
       <c r="E16" s="2">
@@ -902,7 +769,7 @@
         <v>671</v>
       </c>
       <c r="G16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>95.10697923218234</v>
       </c>
       <c r="H16" s="2">
@@ -912,7 +779,7 @@
         <v>1180</v>
       </c>
       <c r="J16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>84.298597514196643</v>
       </c>
       <c r="K16" s="2">
@@ -922,7 +789,7 @@
         <v>586</v>
       </c>
       <c r="M16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>85.667480730366847</v>
       </c>
     </row>
@@ -937,7 +804,7 @@
         <v>9361</v>
       </c>
       <c r="D17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>35.65453321257985</v>
       </c>
       <c r="E17">
@@ -961,14 +828,14 @@
         <v>83.298371981321367</v>
       </c>
       <c r="K17">
-        <v>85.52</v>
+        <v>89.52</v>
       </c>
       <c r="L17">
         <v>429</v>
       </c>
       <c r="M17">
-        <f t="shared" si="7"/>
-        <v>84.429330358873955</v>
+        <f t="shared" si="3"/>
+        <v>88.378316811580873</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -982,7 +849,7 @@
         <v>3248</v>
       </c>
       <c r="D18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>44.947669828157231</v>
       </c>
       <c r="E18">
@@ -992,7 +859,7 @@
         <v>1150</v>
       </c>
       <c r="G18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>94.998623839192874</v>
       </c>
       <c r="H18">
@@ -1002,7 +869,7 @@
         <v>1518</v>
       </c>
       <c r="J18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>89.876910096597371</v>
       </c>
       <c r="K18">
@@ -1012,7 +879,7 @@
         <v>934</v>
       </c>
       <c r="M18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>90.942143160035116</v>
       </c>
     </row>
@@ -1027,7 +894,7 @@
         <v>4094</v>
       </c>
       <c r="D19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>46.435025001178218</v>
       </c>
       <c r="E19" s="3">
@@ -1037,7 +904,7 @@
         <v>651</v>
       </c>
       <c r="G19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>96.136243033764401</v>
       </c>
       <c r="H19" s="3">
@@ -1047,7 +914,7 @@
         <v>1078</v>
       </c>
       <c r="J19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>89.409343663454834</v>
       </c>
       <c r="K19" s="3">
@@ -1057,7 +924,7 @@
         <v>428</v>
       </c>
       <c r="M19">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>92.438701776745134</v>
       </c>
     </row>
@@ -1157,7 +1024,7 @@
         <v>3634</v>
       </c>
       <c r="D27">
-        <f t="shared" ref="D27" si="8">B27*SQRT(1-C27/16927)</f>
+        <f t="shared" ref="D27" si="4">B27*SQRT(1-C27/16927)</f>
         <v>32.496187748926872</v>
       </c>
       <c r="E27" s="5">
@@ -1230,7 +1097,7 @@
         <v>98.43</v>
       </c>
       <c r="E29">
-        <v>2670</v>
+        <v>2270</v>
       </c>
       <c r="F29">
         <v>95.8</v>

--- a/evaluation_metrics.xlsx
+++ b/evaluation_metrics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juhy/Desktop/verl-train/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08E7CD26-1FDB-B04F-8ACE-E3AE2FD793D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD58A7BF-BFCC-5348-85DE-79942C22A00B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="36">
   <si>
     <t>model_path</t>
   </si>
@@ -70,10 +70,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>deepseek-Qwen7B grpo</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>DLER-R1-1.5B-Research</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -100,18 +96,6 @@
     <t>deepseekr1-distill-qwen1.5B</t>
   </si>
   <si>
-    <t>minerva_tokens</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>aime_tokens</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>deepseekr1-distill-qwen1.5B vinilla grpo</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>deepseekr1-distill-qwen7B</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -120,7 +104,67 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>minerva_acc</t>
+    <t>gpqa_diamond</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>tokens</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ours1.5B</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ours7B</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>model</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>aime</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LAC</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>minerva</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>math500</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>gsm8k</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>r1-qwen1.5B</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ours-1.5B</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>r1-qwen7B</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>r1-qwen7B grpo</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>r1-qwen1.5B grpo</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ours-7B</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -128,7 +172,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -157,6 +201,21 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Noto Sans"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -167,13 +226,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -220,17 +279,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -533,10 +598,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="89" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.1640625" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -631,7 +698,7 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B4">
         <v>56.67</v>
@@ -658,9 +725,50 @@
         <v>742</v>
       </c>
     </row>
+    <row r="13" spans="1:13" ht="15">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14">
         <v>36.67</v>
@@ -705,7 +813,7 @@
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15">
         <v>36.67</v>
@@ -749,314 +857,305 @@
       </c>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="2">
+      <c r="A16" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="8">
         <v>36.67</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="8">
         <v>3634</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="9">
         <f t="shared" si="0"/>
         <v>32.496187748926872</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="8">
         <v>97.05</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="8">
         <v>671</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="9">
         <f t="shared" si="1"/>
         <v>95.10697923218234</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="8">
         <v>87.4</v>
       </c>
-      <c r="I16" s="2">
+      <c r="I16" s="8">
         <v>1180</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="9">
         <f t="shared" si="2"/>
         <v>84.298597514196643</v>
       </c>
-      <c r="K16" s="2">
+      <c r="K16" s="8">
         <v>87.19</v>
       </c>
-      <c r="L16" s="2">
+      <c r="L16" s="8">
         <v>586</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="9">
         <f t="shared" si="3"/>
         <v>85.667480730366847</v>
       </c>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17">
+      <c r="A17" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="9">
         <v>53.33</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="9">
         <v>9361</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="9">
         <f t="shared" si="0"/>
         <v>35.65453321257985</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="9">
         <v>96.29</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="9">
         <v>1027</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="9">
         <f>E17*SQRT(1-F17/16927)</f>
         <v>93.323227864775689</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="9">
         <v>90</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="9">
         <v>2427</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="9">
         <f>H17*SQRT(1-I17/16927)</f>
         <v>83.298371981321367</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="9">
         <v>89.52</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="9">
         <v>429</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="9">
         <f t="shared" si="3"/>
         <v>88.378316811580873</v>
       </c>
     </row>
     <row r="18" spans="1:13">
-      <c r="A18" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18">
+      <c r="A18" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="9">
         <v>50</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="9">
         <v>3248</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="9">
         <f t="shared" si="0"/>
         <v>44.947669828157231</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="9">
         <v>98.4</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="9">
         <v>1150</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="9">
         <f t="shared" si="1"/>
         <v>94.998623839192874</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="9">
         <v>94.2</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="9">
         <v>1518</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="9">
         <f t="shared" si="2"/>
         <v>89.876910096597371</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="9">
         <v>93.56</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="9">
         <v>934</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="9">
         <f t="shared" si="3"/>
         <v>90.942143160035116</v>
       </c>
     </row>
     <row r="19" spans="1:13">
-      <c r="A19" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="3">
+      <c r="A19" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="9">
         <v>53.33</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="9">
         <v>4094</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="9">
         <f t="shared" si="0"/>
         <v>46.435025001178218</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="9">
         <v>98.04</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="9">
         <v>651</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="9">
         <f t="shared" si="1"/>
         <v>96.136243033764401</v>
       </c>
-      <c r="H19" s="3">
+      <c r="H19" s="9">
         <v>92.4</v>
       </c>
-      <c r="I19" s="3">
+      <c r="I19" s="9">
         <v>1078</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="9">
         <f t="shared" si="2"/>
         <v>89.409343663454834</v>
       </c>
-      <c r="K19" s="3">
+      <c r="K19" s="9">
         <v>93.63</v>
       </c>
-      <c r="L19" s="3">
+      <c r="L19" s="9">
         <v>428</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="9">
         <f t="shared" si="3"/>
         <v>92.438701776745134</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="15" thickBot="1">
-      <c r="B24" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D24" s="1" t="s">
+    <row r="24" spans="1:13" ht="16" thickBot="1">
+      <c r="A24" t="s">
         <v>24</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J24" s="1"/>
+      <c r="B24" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J24" s="7"/>
     </row>
     <row r="25" spans="1:13" ht="16" thickBot="1">
-      <c r="A25" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B25" s="4">
+      <c r="A25" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" s="3">
         <v>0.33329999999999999</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="3">
         <v>16927</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="3">
         <v>0.96379999999999999</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E25" s="3">
         <v>3054</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F25" s="3">
         <v>0.874</v>
       </c>
-      <c r="G25" s="4">
+      <c r="G25" s="3">
         <v>5485</v>
       </c>
-      <c r="H25" s="4">
+      <c r="H25" s="3">
         <v>0.84609999999999996</v>
       </c>
-      <c r="I25" s="4">
+      <c r="I25" s="3">
         <v>1909</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="16" thickBot="1">
-      <c r="A26" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B26" s="4">
+      <c r="A26" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="3">
         <v>0.4</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="3">
         <v>15127</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="3">
         <v>0.97560000000000002</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E26" s="3">
         <v>2953</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F26" s="3">
         <v>0.88600000000000001</v>
       </c>
-      <c r="G26" s="4">
+      <c r="G26" s="3">
         <v>5135</v>
       </c>
-      <c r="H26" s="4">
+      <c r="H26" s="3">
         <v>0.87939999999999996</v>
       </c>
-      <c r="I26" s="4">
+      <c r="I26" s="3">
         <v>2202</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="15" thickBot="1">
-      <c r="A27" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="5">
+      <c r="A27" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="4">
         <v>36.67</v>
       </c>
-      <c r="C27" s="5">
+      <c r="C27" s="4">
         <v>3634</v>
       </c>
-      <c r="D27">
-        <f t="shared" ref="D27" si="4">B27*SQRT(1-C27/16927)</f>
-        <v>32.496187748926872</v>
-      </c>
-      <c r="E27" s="5">
+      <c r="D27" s="4">
         <v>97.05</v>
       </c>
-      <c r="F27" s="5">
+      <c r="E27" s="4">
         <v>671</v>
       </c>
-      <c r="G27">
-        <f>E27*SQRT(1-F27/3054)</f>
-        <v>85.72806960369762</v>
-      </c>
-      <c r="H27" s="5">
+      <c r="F27" s="4">
         <v>87.4</v>
       </c>
-      <c r="I27" s="5">
+      <c r="G27" s="4">
         <v>1180</v>
       </c>
-      <c r="J27">
-        <f>H27*SQRT(1-I27/5485)</f>
-        <v>77.430077611156022</v>
-      </c>
-      <c r="K27" s="5">
+      <c r="H27" s="4">
         <v>87.19</v>
       </c>
-      <c r="L27" s="5">
+      <c r="I27" s="4">
         <v>586</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="16" thickBot="1">
-      <c r="A28" s="4" t="s">
-        <v>22</v>
+      <c r="A28" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="B28">
         <v>56.67</v>
@@ -1085,7 +1184,7 @@
     </row>
     <row r="29" spans="1:13">
       <c r="A29" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="B29">
         <v>56.67</v>
@@ -1106,45 +1205,101 @@
         <v>4886</v>
       </c>
       <c r="H29">
-        <v>92.87</v>
+        <v>93</v>
       </c>
       <c r="I29">
         <v>1650</v>
       </c>
     </row>
     <row r="30" spans="1:13">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" s="2">
+        <v>53.33</v>
+      </c>
+      <c r="C30" s="2">
+        <v>4094</v>
+      </c>
+      <c r="D30" s="2">
+        <v>98.04</v>
+      </c>
+      <c r="E30" s="2">
+        <v>651</v>
+      </c>
+      <c r="F30" s="2">
+        <v>92.4</v>
+      </c>
+      <c r="G30" s="2">
+        <v>1078</v>
+      </c>
+      <c r="H30" s="2">
+        <v>93.63</v>
+      </c>
+      <c r="I30" s="2">
+        <v>428</v>
+      </c>
+      <c r="J30" s="2"/>
+      <c r="M30" s="2"/>
+    </row>
+    <row r="34" spans="1:3" ht="15" thickBot="1">
+      <c r="A34" t="s">
+        <v>24</v>
+      </c>
+      <c r="B34" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="16" thickBot="1">
+      <c r="A35" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B30" s="3">
-        <v>53.33</v>
-      </c>
-      <c r="C30" s="3">
-        <v>4094</v>
-      </c>
-      <c r="D30" s="3">
-        <v>98.04</v>
-      </c>
-      <c r="E30" s="3">
-        <v>651</v>
-      </c>
-      <c r="F30" s="3">
-        <v>92.4</v>
-      </c>
-      <c r="G30" s="3">
-        <v>1078</v>
-      </c>
-      <c r="H30" s="3">
-        <v>93.63</v>
-      </c>
-      <c r="I30" s="3">
-        <v>428</v>
-      </c>
-      <c r="J30" s="3"/>
-      <c r="M30" s="3"/>
+      <c r="B35">
+        <v>0.30809999999999998</v>
+      </c>
+      <c r="C35">
+        <v>10308</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="15" thickBot="1">
+      <c r="A36" t="s">
+        <v>22</v>
+      </c>
+      <c r="B36">
+        <v>0.33839999999999998</v>
+      </c>
+      <c r="C36">
+        <v>5089</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="16" thickBot="1">
+      <c r="A37" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B37">
+        <v>0.49490000000000001</v>
+      </c>
+      <c r="C37" s="5">
+        <v>8570</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>23</v>
+      </c>
+      <c r="B38">
+        <v>0.48480000000000001</v>
+      </c>
+      <c r="C38">
+        <v>4944</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>